--- a/feature_sets.xlsx
+++ b/feature_sets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,7 +519,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Einfachstes Momentum-Signal (Jegadeesh &amp; Titman, 1993). Vormals B1.</t>
+          <t>Einfachstes Momentum-Signal (Jegadeesh &amp; Titman, 1993).</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Kurz- und mittelfristiges Momentum (Moskowitz et al., 2012). Vormals E1.</t>
+          <t>Kurz- und mittelfristiges Momentum (Moskowitz et al., 2012).</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Momentum mit Volatilitätsregime (Ang et al., 2006). Vormals E2.</t>
+          <t>Momentum mit Volatilitätsregime (Ang et al., 2006).</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Momentum mit Volumenänderung (Campbell et al., 1993). Vormals E3.</t>
+          <t>Momentum mit Volumenänderung (Campbell et al., 1993).</t>
         </is>
       </c>
     </row>
@@ -659,29 +659,29 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alle ökonomischen Features. Markt+Size+Momentum (Liu et al., 2022). Vormals E4.</t>
+          <t>Alle ökonomischen Features. Markt+Size+Momentum (Liu et al., 2022).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SV1</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sentiment_vader</t>
+          <t>sentiment_cryptobert</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>vader</t>
+          <t>cryptobert</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Title Mean</t>
+          <t>CryptoBERT Title Mean</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -689,7 +689,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>vader_title_score_mean</t>
+          <t>cryptobert_title_score_mean</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SV2</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sentiment_vader</t>
+          <t>sentiment_cryptobert</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>vader</t>
+          <t>cryptobert</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Title + Bullishness</t>
+          <t>CryptoBERT Title + Bullishness</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -724,7 +724,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>vader_title_score_mean,vader_bullishness_ratio</t>
+          <t>cryptobert_title_score_mean,cryptobert_bullishness_ratio</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -736,22 +736,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SV3</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sentiment_vader</t>
+          <t>sentiment_cryptobert</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>vader</t>
+          <t>cryptobert</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Rich Sentiment</t>
+          <t>CryptoBERT Rich Sentiment</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -759,7 +759,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>vader_title_score_mean,vader_title_score_weighted_mean,vader_bullishness_ratio,vader_title_score_std,post_count</t>
+          <t>cryptobert_title_score_mean,cryptobert_title_score_weighted_mean,cryptobert_bullishness_ratio,cryptobert_title_score_std,post_count</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -771,22 +771,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SF1</t>
+          <t>SV1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sentiment_finbert</t>
+          <t>sentiment_vader</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>finbert</t>
+          <t>vader</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Title Mean</t>
+          <t>VADER Title Mean</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -794,7 +794,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>finbert_title_score_mean</t>
+          <t>vader_title_score_mean</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -806,22 +806,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SF2</t>
+          <t>SV2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sentiment_finbert</t>
+          <t>sentiment_vader</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>finbert</t>
+          <t>vader</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Title + Bullishness</t>
+          <t>VADER Title + Bullishness</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -829,7 +829,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>finbert_title_score_mean,finbert_bullishness_ratio</t>
+          <t>vader_title_score_mean,vader_bullishness_ratio</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -841,22 +841,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SF3</t>
+          <t>SV3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sentiment_finbert</t>
+          <t>sentiment_vader</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>finbert</t>
+          <t>vader</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Rich Sentiment</t>
+          <t>VADER Rich Sentiment</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -864,7 +864,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>finbert_title_score_mean,finbert_title_score_weighted_mean,finbert_bullishness_ratio,finbert_title_score_std,post_count</t>
+          <t>vader_title_score_mean,vader_title_score_weighted_mean,vader_bullishness_ratio,vader_title_score_std,post_count</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -876,12 +876,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SC1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sentiment_cryptobert</t>
+          <t>combined_cryptobert</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Title Mean</t>
+          <t>B1 + S1 (Hist.-Maj. baseline + simple sentiment)</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -904,19 +904,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Einfachstes Sentiment-Signal (Kraaijeveld &amp; De Smedt, 2020).</t>
+          <t>Combined CryptoBERT: B1 + S1.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SC2</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sentiment_cryptobert</t>
+          <t>combined_cryptobert</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -926,32 +926,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Title + Bullishness</t>
+          <t>B2 + S2 (lag return + medium sentiment)</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>cryptobert_title_score_mean,cryptobert_bullishness_ratio</t>
+          <t>log_return_t,cryptobert_title_score_mean,cryptobert_bullishness_ratio</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Level + Richtungskonsens (Kraaijeveld &amp; De Smedt, 2020).</t>
+          <t>Combined CryptoBERT: B2 + S2.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SC3</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sentiment_cryptobert</t>
+          <t>combined_cryptobert</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -961,102 +961,102 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Rich Sentiment</t>
+          <t>B3 + S3 (momentum + rich sentiment)</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>cryptobert_title_score_mean,cryptobert_title_score_weighted_mean,cryptobert_bullishness_ratio,cryptobert_title_score_std,post_count</t>
+          <t>log_return_t,cum_log_return_7,cum_log_return_14,cryptobert_title_score_mean,cryptobert_title_score_weighted_mean,cryptobert_bullishness_ratio,cryptobert_title_score_std,post_count</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alle Dimensionen: Level, Gewichtung, Richtung, Divergenz, Volumen.</t>
+          <t>Combined CryptoBERT: B3 + S3.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>combined</t>
+          <t>combined_cryptobert</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>vader</t>
+          <t>cryptobert</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Title + Mom + Vol</t>
+          <t>B4 + S3 (momentum+vol + rich sentiment)</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>vader_title_score_mean,log_return_t,cum_log_return_7,cum_log_return_14,realized_vol_14</t>
+          <t>log_return_t,cum_log_return_7,cum_log_return_14,realized_vol_14,cryptobert_title_score_mean,cryptobert_title_score_weighted_mean,cryptobert_bullishness_ratio,cryptobert_title_score_std,post_count</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Einfachstes Sentiment + B4 (Mom+Vol). = SV1 + B4.</t>
+          <t>Combined CryptoBERT: B4 + S3.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>combined</t>
+          <t>combined_cryptobert</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>finbert</t>
+          <t>cryptobert</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Title + Mom + Vol</t>
+          <t>B5 + S3 (momentum+volume + rich sentiment)</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>finbert_title_score_mean,log_return_t,cum_log_return_7,cum_log_return_14,realized_vol_14</t>
+          <t>log_return_t,cum_log_return_7,cum_log_return_14,volume_diff,cryptobert_title_score_mean,cryptobert_title_score_weighted_mean,cryptobert_bullishness_ratio,cryptobert_title_score_std,post_count</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Einfachstes Sentiment + B4 (Mom+Vol). = SF1 + B4.</t>
+          <t>Combined CryptoBERT: B5 + S3.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>combined</t>
+          <t>combined_cryptobert</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1066,32 +1066,32 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Title + Mom + Vol</t>
+          <t>B6 + S3 (full economic + rich sentiment)</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>cryptobert_title_score_mean,log_return_t,cum_log_return_7,cum_log_return_14,realized_vol_14</t>
+          <t>log_return_t,cum_log_return_7,cum_log_return_14,realized_vol_14,volume_diff,market_cap_t,cryptobert_title_score_mean,cryptobert_title_score_weighted_mean,cryptobert_bullishness_ratio,cryptobert_title_score_std,post_count</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Einfachstes Sentiment + B4 (Mom+Vol). = SC1 + B4.</t>
+          <t>Combined CryptoBERT: B6 + S3.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>CV1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>combined</t>
+          <t>combined_vader</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1101,77 +1101,77 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Title + Bullishness + Full Econ</t>
+          <t>B1 + SV1 (Hist.-Maj. baseline + simple sentiment)</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>vader_title_score_mean,vader_bullishness_ratio,log_return_t,cum_log_return_7,cum_log_return_14,realized_vol_14,volume_diff,market_cap_t</t>
+          <t>vader_title_score_mean</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sentiment Kern + B6 (Full Economic). = SV2 + B6.</t>
+          <t>Combined VADER: B1 + SV1.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>CV2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>combined</t>
+          <t>combined_vader</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>finbert</t>
+          <t>vader</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Title + Bullishness + Full Econ</t>
+          <t>B2 + SV2 (lag return + medium sentiment)</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>finbert_title_score_mean,finbert_bullishness_ratio,log_return_t,cum_log_return_7,cum_log_return_14,realized_vol_14,volume_diff,market_cap_t</t>
+          <t>log_return_t,vader_title_score_mean,vader_bullishness_ratio</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sentiment Kern + B6 (Full Economic). = SF2 + B6.</t>
+          <t>Combined VADER: B2 + SV2.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>CV3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>combined</t>
+          <t>combined_vader</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>cryptobert</t>
+          <t>vader</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Title + Bullishness + Full Econ</t>
+          <t>B3 + SV3 (momentum + rich sentiment)</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1179,24 +1179,24 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>cryptobert_title_score_mean,cryptobert_bullishness_ratio,log_return_t,cum_log_return_7,cum_log_return_14,realized_vol_14,volume_diff,market_cap_t</t>
+          <t>log_return_t,cum_log_return_7,cum_log_return_14,vader_title_score_mean,vader_title_score_weighted_mean,vader_bullishness_ratio,vader_title_score_std,post_count</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sentiment Kern + B6 (Full Economic). = SC2 + B6.</t>
+          <t>Combined VADER: B3 + SV3.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>CV4</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>combined</t>
+          <t>combined_vader</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1206,77 +1206,77 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Rich Sentiment + Full Econ</t>
+          <t>B4 + SV3 (momentum+vol + rich sentiment)</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>vader_title_score_mean,vader_title_score_weighted_mean,vader_bullishness_ratio,vader_title_score_std,post_count,log_return_t,cum_log_return_7,cum_log_return_14,realized_vol_14,volume_diff,market_cap_t</t>
+          <t>log_return_t,cum_log_return_7,cum_log_return_14,realized_vol_14,vader_title_score_mean,vader_title_score_weighted_mean,vader_bullishness_ratio,vader_title_score_std,post_count</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Vollständige Sentiment-Batterie + B6 (Full Economic). = SV3 + B6.</t>
+          <t>Combined VADER: B4 + SV3.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>CV5</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>combined</t>
+          <t>combined_vader</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>finbert</t>
+          <t>vader</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Rich Sentiment + Full Econ</t>
+          <t>B5 + SV3 (momentum+volume + rich sentiment)</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>finbert_title_score_mean,finbert_title_score_weighted_mean,finbert_bullishness_ratio,finbert_title_score_std,post_count,log_return_t,cum_log_return_7,cum_log_return_14,realized_vol_14,volume_diff,market_cap_t</t>
+          <t>log_return_t,cum_log_return_7,cum_log_return_14,volume_diff,vader_title_score_mean,vader_title_score_weighted_mean,vader_bullishness_ratio,vader_title_score_std,post_count</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Vollständige Sentiment-Batterie + B6 (Full Economic). = SF3 + B6.</t>
+          <t>Combined VADER: B5 + SV3.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>CV6</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>combined</t>
+          <t>combined_vader</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>cryptobert</t>
+          <t>vader</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Rich Sentiment + Full Econ</t>
+          <t>B6 + SV3 (full economic + rich sentiment)</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>cryptobert_title_score_mean,cryptobert_title_score_weighted_mean,cryptobert_bullishness_ratio,cryptobert_title_score_std,post_count,log_return_t,cum_log_return_7,cum_log_return_14,realized_vol_14,volume_diff,market_cap_t</t>
+          <t>log_return_t,cum_log_return_7,cum_log_return_14,realized_vol_14,volume_diff,market_cap_t,vader_title_score_mean,vader_title_score_weighted_mean,vader_bullishness_ratio,vader_title_score_std,post_count</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Vollständige Sentiment-Batterie + B6 (Full Economic). = SC3 + B6.</t>
+          <t>Combined VADER: B6 + SV3.</t>
         </is>
       </c>
     </row>
@@ -1311,20 +1311,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Multi Title + Mom + Vol</t>
+          <t>B1 + S1 + SV1 (multi baseline)</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>vader_title_score_mean,finbert_title_score_mean,cryptobert_title_score_mean,log_return_t,cum_log_return_7,cum_log_return_14,realized_vol_14</t>
+          <t>cryptobert_title_score_mean,vader_title_score_mean</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Konsens dreier Sentiment-Quellen (V+F+C) auf Level 1 + B4 (Mom+Vol). = SV1 + SF1 + SC1 + B4.</t>
+          <t>Multi-source: B1 + S1 + SV1.</t>
         </is>
       </c>
     </row>
@@ -1346,20 +1346,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Multi Title + Bullishness + Full Econ</t>
+          <t>B2 + S2 + SV2 (multi medium)</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>vader_title_score_mean,vader_bullishness_ratio,finbert_title_score_mean,finbert_bullishness_ratio,cryptobert_title_score_mean,cryptobert_bullishness_ratio,log_return_t,cum_log_return_7,cum_log_return_14,realized_vol_14,volume_diff,market_cap_t</t>
+          <t>log_return_t,cryptobert_title_score_mean,cryptobert_bullishness_ratio,vader_title_score_mean,vader_bullishness_ratio</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Konsens dreier Sentiment-Quellen (V+F+C) auf Level 2 + B6 (Full Econ). = SV2 + SF2 + SC2 + B6.</t>
+          <t>Multi-source: B2 + S2 + SV2.</t>
         </is>
       </c>
     </row>
@@ -1381,20 +1381,125 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Multi Rich + Full Econ</t>
+          <t>B3 + S3 + SV3 (multi rich)</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>vader_title_score_mean,vader_title_score_weighted_mean,vader_bullishness_ratio,vader_title_score_std,post_count,finbert_title_score_mean,finbert_title_score_weighted_mean,finbert_bullishness_ratio,finbert_title_score_std,cryptobert_title_score_mean,cryptobert_title_score_weighted_mean,cryptobert_bullishness_ratio,cryptobert_title_score_std,log_return_t,cum_log_return_7,cum_log_return_14,realized_vol_14,volume_diff,market_cap_t</t>
+          <t>log_return_t,cum_log_return_7,cum_log_return_14,cryptobert_title_score_mean,cryptobert_title_score_weighted_mean,cryptobert_bullishness_ratio,cryptobert_title_score_std,post_count,vader_title_score_mean,vader_title_score_weighted_mean,vader_bullishness_ratio,vader_title_score_std</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Konsens dreier Sentiment-Quellen (V+F+C) auf Level 3 + B6 (Full Econ). = SV3 + SF3 + SC3 + B6.</t>
+          <t>Multi-source: B3 + S3 + SV3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>multi</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>multi</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>B4 + S3 + SV3 (multi rich + mom+vol)</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>13</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>log_return_t,cum_log_return_7,cum_log_return_14,realized_vol_14,cryptobert_title_score_mean,cryptobert_title_score_weighted_mean,cryptobert_bullishness_ratio,cryptobert_title_score_std,post_count,vader_title_score_mean,vader_title_score_weighted_mean,vader_bullishness_ratio,vader_title_score_std</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Multi-source: B4 + S3 + SV3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>multi</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>multi</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>B5 + S3 + SV3 (multi rich + mom+volume)</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>13</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>log_return_t,cum_log_return_7,cum_log_return_14,volume_diff,cryptobert_title_score_mean,cryptobert_title_score_weighted_mean,cryptobert_bullishness_ratio,cryptobert_title_score_std,post_count,vader_title_score_mean,vader_title_score_weighted_mean,vader_bullishness_ratio,vader_title_score_std</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Multi-source: B5 + S3 + SV3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>multi</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>multi</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>B6 + S3 + SV3 (multi rich + full economic)</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>15</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>log_return_t,cum_log_return_7,cum_log_return_14,realized_vol_14,volume_diff,market_cap_t,cryptobert_title_score_mean,cryptobert_title_score_weighted_mean,cryptobert_bullishness_ratio,cryptobert_title_score_std,post_count,vader_title_score_mean,vader_title_score_weighted_mean,vader_bullishness_ratio,vader_title_score_std</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Multi-source: B6 + S3 + SV3.</t>
         </is>
       </c>
     </row>
